--- a/database/event/5901/event_5901_evp_summary.xlsx
+++ b/database/event/5901/event_5901_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.7311</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6219</v>
+        <v>8.182399999999999</v>
       </c>
       <c r="I2" t="n">
         <v>9.201000000000001</v>
@@ -548,7 +548,7 @@
         <v>1.7311</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E3" t="n">
         <v>6.4635</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>9.5387</v>
+        <v>9.0524</v>
       </c>
       <c r="I3" t="n">
         <v>10.1794</v>
@@ -594,7 +594,7 @@
         <v>1.7311</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E4" t="n">
         <v>6.4635</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1082</v>
+        <v>10.5814</v>
       </c>
       <c r="I4" t="n">
         <v>11.7994</v>
@@ -640,7 +640,7 @@
         <v>1.7311</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E5" t="n">
         <v>6.4635</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4056</v>
+        <v>8.097200000000001</v>
       </c>
       <c r="I5" t="n">
         <v>8.805099999999999</v>
@@ -686,7 +686,7 @@
         <v>1.7311</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E6" t="n">
         <v>6.4635</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3458</v>
+        <v>9.8184</v>
       </c>
       <c r="I6" t="n">
         <v>11.0407</v>
@@ -732,7 +732,7 @@
         <v>1.7311</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E7" t="n">
         <v>6.4635</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.6366</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>10.0946</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4827</v>
+        <v>5.3354</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4684</v>
+        <v>1.429</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7935</v>
+        <v>1.6817</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4827</v>
+        <v>5.3354</v>
       </c>
       <c r="F8" t="n">
-        <v>5.4827</v>
+        <v>5.3354</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2938</v>
+        <v>6.0629</v>
       </c>
       <c r="I8" t="n">
         <v>6.5929</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.223</v>
+        <v>5.0717</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3989</v>
+        <v>1.3584</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6886</v>
+        <v>1.5767</v>
       </c>
       <c r="E9" t="n">
-        <v>5.223</v>
+        <v>5.0717</v>
       </c>
       <c r="F9" t="n">
-        <v>5.223</v>
+        <v>5.0717</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8865</v>
+        <v>5.6494</v>
       </c>
       <c r="I9" t="n">
         <v>6.195</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.8117</v>
+        <v>4.6413</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2887</v>
+        <v>1.2431</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5225</v>
+        <v>1.4052</v>
       </c>
       <c r="E10" t="n">
-        <v>4.8117</v>
+        <v>4.6413</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8117</v>
+        <v>4.6413</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2417</v>
+        <v>4.9745</v>
       </c>
       <c r="I10" t="n">
         <v>5.5938</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.5291</v>
+        <v>4.4168</v>
       </c>
       <c r="C11" t="n">
-        <v>1.213</v>
+        <v>1.183</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4083</v>
+        <v>1.3157</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5291</v>
+        <v>4.4168</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5291</v>
+        <v>4.4168</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7986</v>
+        <v>4.6226</v>
       </c>
       <c r="I11" t="n">
         <v>5.0267</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.3061</v>
+        <v>4.1919</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1533</v>
+        <v>1.1227</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3182</v>
+        <v>1.2261</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3061</v>
+        <v>4.1919</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3061</v>
+        <v>4.1919</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.449</v>
+        <v>4.2698</v>
       </c>
       <c r="I12" t="n">
         <v>4.6821</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.078</v>
+        <v>3.9856</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0922</v>
+        <v>1.0675</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2261</v>
+        <v>1.144</v>
       </c>
       <c r="E13" t="n">
-        <v>4.078</v>
+        <v>3.9856</v>
       </c>
       <c r="F13" t="n">
-        <v>4.078</v>
+        <v>3.9856</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0913</v>
+        <v>3.9856</v>
       </c>
       <c r="I13" t="n">
         <v>4.2265</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9885</v>
+        <v>3.9001</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0682</v>
+        <v>1.0446</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1899</v>
+        <v>1.1099</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9885</v>
+        <v>3.9001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9885</v>
+        <v>3.9001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9885</v>
+        <v>3.9001</v>
       </c>
       <c r="I14" t="n">
         <v>4.1012</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9778</v>
+        <v>3.8448</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0654</v>
+        <v>1.0298</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1856</v>
+        <v>1.0879</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9778</v>
+        <v>3.8448</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9778</v>
+        <v>3.8448</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9778</v>
+        <v>3.8448</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1669</v>
+        <v>4.146</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>409</v>
+        <v>463</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1669</v>
+        <v>4.146</v>
       </c>
       <c r="N15" t="n">
-        <v>409</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.9763</v>
+        <v>3.8319</v>
       </c>
       <c r="C16" t="n">
-        <v>1.065</v>
+        <v>1.0263</v>
       </c>
       <c r="D16" t="n">
-        <v>1.185</v>
+        <v>1.0827</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9763</v>
+        <v>3.8319</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9763</v>
+        <v>3.8319</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9763</v>
+        <v>3.8319</v>
       </c>
       <c r="I16" t="n">
-        <v>4.146</v>
+        <v>4.1669</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.146</v>
+        <v>4.1669</v>
       </c>
       <c r="N16" t="n">
-        <v>463</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.9109</v>
+        <v>3.7534</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0475</v>
+        <v>1.0053</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1586</v>
+        <v>1.0514</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9109</v>
+        <v>3.7534</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9109</v>
+        <v>3.7534</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9109</v>
+        <v>3.7534</v>
       </c>
       <c r="I17" t="n">
         <v>4.1159</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.797</v>
+        <v>3.6034</v>
       </c>
       <c r="C18" t="n">
-        <v>1.017</v>
+        <v>0.9651</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1125</v>
+        <v>0.9917</v>
       </c>
       <c r="E18" t="n">
-        <v>3.797</v>
+        <v>3.6034</v>
       </c>
       <c r="F18" t="n">
-        <v>3.797</v>
+        <v>3.6034</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.797</v>
+        <v>3.6034</v>
       </c>
       <c r="I18" t="n">
         <v>4.0521</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5764</v>
+        <v>3.4324</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9579</v>
+        <v>0.9193</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0234</v>
+        <v>0.9236</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5764</v>
+        <v>3.4324</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5764</v>
+        <v>3.4324</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5764</v>
+        <v>3.4324</v>
       </c>
       <c r="I19" t="n">
         <v>3.7639</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.5706</v>
+        <v>3.4268</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9563</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0211</v>
+        <v>0.9213</v>
       </c>
       <c r="E20" t="n">
-        <v>3.5706</v>
+        <v>3.4268</v>
       </c>
       <c r="F20" t="n">
-        <v>3.5706</v>
+        <v>3.4268</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5706</v>
+        <v>3.4268</v>
       </c>
       <c r="I20" t="n">
         <v>3.7577</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.4633</v>
+        <v>3.2868</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9276</v>
+        <v>0.8803</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9777</v>
+        <v>0.8656</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4633</v>
+        <v>3.2868</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4633</v>
+        <v>3.2868</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4633</v>
+        <v>3.2868</v>
       </c>
       <c r="I21" t="n">
         <v>3.696</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.2433</v>
+        <v>3.136</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8687</v>
+        <v>0.8399</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8889</v>
+        <v>0.8055</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2433</v>
+        <v>3.136</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2433</v>
+        <v>3.136</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2433</v>
+        <v>3.136</v>
       </c>
       <c r="I22" t="n">
         <v>3.3817</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9251</v>
+        <v>2.8496</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7834</v>
+        <v>0.7632</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7603</v>
+        <v>0.6914</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9251</v>
+        <v>2.8496</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9251</v>
+        <v>2.8496</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9251</v>
+        <v>2.8496</v>
       </c>
       <c r="I23" t="n">
         <v>3.0217</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7945</v>
+        <v>2.652</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7103</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7076</v>
+        <v>0.6126</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7945</v>
+        <v>2.652</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7945</v>
+        <v>2.652</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7945</v>
+        <v>2.652</v>
       </c>
       <c r="I24" t="n">
         <v>2.9822</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5504</v>
+        <v>2.4846</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6831</v>
+        <v>0.6655</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6089</v>
+        <v>0.546</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5504</v>
+        <v>2.4846</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5504</v>
+        <v>2.4846</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5504</v>
+        <v>2.4846</v>
       </c>
       <c r="I25" t="n">
         <v>2.6347</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.459</v>
+        <v>2.4135</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6586</v>
+        <v>0.6464</v>
       </c>
       <c r="D26" t="n">
-        <v>0.572</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.459</v>
+        <v>2.4135</v>
       </c>
       <c r="F26" t="n">
-        <v>2.459</v>
+        <v>2.4135</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.459</v>
+        <v>2.4135</v>
       </c>
       <c r="I26" t="n">
         <v>2.5168</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3076</v>
+        <v>2.2734</v>
       </c>
       <c r="C27" t="n">
-        <v>0.618</v>
+        <v>0.6089</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5109</v>
+        <v>0.4618</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3076</v>
+        <v>2.2734</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3076</v>
+        <v>2.2734</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3076</v>
+        <v>2.2734</v>
       </c>
       <c r="I27" t="n">
         <v>2.3509</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2944</v>
+        <v>2.2603</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6145</v>
+        <v>0.6054</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4566</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2944</v>
+        <v>2.2603</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2944</v>
+        <v>2.2603</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2944</v>
+        <v>2.2603</v>
       </c>
       <c r="I28" t="n">
         <v>2.3374</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.1855</v>
+        <v>2.1291</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5853</v>
+        <v>0.5702</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4615</v>
+        <v>0.4043</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1855</v>
+        <v>2.1291</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1855</v>
+        <v>2.1291</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1855</v>
+        <v>2.1291</v>
       </c>
       <c r="I29" t="n">
         <v>2.2577</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0952</v>
+        <v>2.0411</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5612</v>
+        <v>0.5467</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4251</v>
+        <v>0.3693</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0952</v>
+        <v>2.0411</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0952</v>
+        <v>2.0411</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0952</v>
+        <v>2.0411</v>
       </c>
       <c r="I30" t="n">
         <v>2.1644</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>iDISBALANCE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.0328</v>
+        <v>1.9811</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5444</v>
+        <v>0.5306</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3998</v>
+        <v>0.3454</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0328</v>
+        <v>1.9811</v>
       </c>
       <c r="F31" t="n">
-        <v>2.0328</v>
+        <v>1.9811</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.0328</v>
+        <v>1.9811</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1393</v>
+        <v>2.0658</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.1393</v>
+        <v>2.0658</v>
       </c>
       <c r="N31" t="n">
-        <v>359</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iDISBALANCE</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.0184</v>
+        <v>1.9509</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5406</v>
+        <v>0.5225</v>
       </c>
       <c r="D32" t="n">
-        <v>0.394</v>
+        <v>0.3333</v>
       </c>
       <c r="E32" t="n">
-        <v>2.0184</v>
+        <v>1.9509</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0184</v>
+        <v>1.9509</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.0184</v>
+        <v>1.9509</v>
       </c>
       <c r="I32" t="n">
-        <v>2.0658</v>
+        <v>2.1393</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.0658</v>
+        <v>2.1393</v>
       </c>
       <c r="N32" t="n">
-        <v>327</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33">
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.9867</v>
+        <v>1.9499</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5321</v>
+        <v>0.5222</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3812</v>
+        <v>0.3329</v>
       </c>
       <c r="E33" t="n">
-        <v>1.9867</v>
+        <v>1.9499</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9867</v>
+        <v>1.9499</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.9867</v>
+        <v>1.9499</v>
       </c>
       <c r="I33" t="n">
         <v>2.0334</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.9745</v>
+        <v>1.9236</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5288</v>
+        <v>0.5152</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3763</v>
+        <v>0.3225</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9745</v>
+        <v>1.9236</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9745</v>
+        <v>1.9236</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9745</v>
+        <v>1.9236</v>
       </c>
       <c r="I34" t="n">
         <v>2.0398</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.8778</v>
+        <v>1.85</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5029</v>
+        <v>0.4955</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3372</v>
+        <v>0.2931</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8778</v>
+        <v>1.85</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8778</v>
+        <v>1.85</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8778</v>
+        <v>1.85</v>
       </c>
       <c r="I35" t="n">
         <v>1.913</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.7437</v>
+        <v>1.6987</v>
       </c>
       <c r="C36" t="n">
-        <v>0.467</v>
+        <v>0.455</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2831</v>
+        <v>0.2329</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7437</v>
+        <v>1.6987</v>
       </c>
       <c r="F36" t="n">
-        <v>1.7437</v>
+        <v>1.6987</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.7437</v>
+        <v>1.6987</v>
       </c>
       <c r="I36" t="n">
         <v>1.8013</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.7424</v>
+        <v>1.6785</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4667</v>
+        <v>0.4496</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2825</v>
+        <v>0.2248</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7424</v>
+        <v>1.6785</v>
       </c>
       <c r="F37" t="n">
-        <v>1.7424</v>
+        <v>1.6785</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.7424</v>
+        <v>1.6785</v>
       </c>
       <c r="I37" t="n">
         <v>1.8252</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6664</v>
+        <v>1.6478</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4463</v>
+        <v>0.4413</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2518</v>
+        <v>0.2126</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6664</v>
+        <v>1.6478</v>
       </c>
       <c r="F38" t="n">
-        <v>1.6664</v>
+        <v>1.6478</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.6664</v>
+        <v>1.6478</v>
       </c>
       <c r="I38" t="n">
         <v>1.6898</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.4946</v>
+        <v>1.4834</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4003</v>
+        <v>0.3973</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1824</v>
+        <v>0.1471</v>
       </c>
       <c r="E39" t="n">
-        <v>1.4946</v>
+        <v>1.4834</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4946</v>
+        <v>1.4834</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.4946</v>
+        <v>1.4834</v>
       </c>
       <c r="I39" t="n">
         <v>1.5085</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Electro</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.4387</v>
+        <v>1.421</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3853</v>
+        <v>0.3806</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1598</v>
+        <v>0.1222</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4387</v>
+        <v>1.421</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4387</v>
+        <v>1.421</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.4387</v>
+        <v>1.421</v>
       </c>
       <c r="I40" t="n">
-        <v>1.4862</v>
+        <v>1.4572</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>330</v>
+        <v>208</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4862</v>
+        <v>1.4572</v>
       </c>
       <c r="N40" t="n">
-        <v>330</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Electro</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.437</v>
+        <v>1.4015</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3849</v>
+        <v>0.3754</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1592</v>
+        <v>0.1144</v>
       </c>
       <c r="E41" t="n">
-        <v>1.437</v>
+        <v>1.4015</v>
       </c>
       <c r="F41" t="n">
-        <v>1.437</v>
+        <v>1.4015</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.437</v>
+        <v>1.4015</v>
       </c>
       <c r="I41" t="n">
-        <v>1.4572</v>
+        <v>1.4862</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4572</v>
+        <v>1.4862</v>
       </c>
       <c r="N41" t="n">
-        <v>208</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42">
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2367</v>
+        <v>1.2275</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3312</v>
+        <v>0.3288</v>
       </c>
       <c r="D42" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0451</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2367</v>
+        <v>1.2275</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2367</v>
+        <v>1.2275</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2367</v>
+        <v>1.2275</v>
       </c>
       <c r="I42" t="n">
         <v>1.2482</v>
@@ -2388,7 +2388,7 @@
         <v>0.2185</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1189</v>
       </c>
       <c r="E43" t="n">
         <v>0.8158</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5636</v>
+        <v>0.5531</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1509</v>
+        <v>0.1481</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1937</v>
+        <v>-0.2236</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5636</v>
+        <v>0.5531</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5636</v>
+        <v>0.5531</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5636</v>
+        <v>0.5531</v>
       </c>
       <c r="I44" t="n">
         <v>0.5768</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5326</v>
+        <v>0.5228</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1426</v>
+        <v>0.14</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2062</v>
+        <v>-0.2356</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5326</v>
+        <v>0.5228</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5326</v>
+        <v>0.5228</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5326</v>
+        <v>0.5228</v>
       </c>
       <c r="I45" t="n">
         <v>0.5451</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4324</v>
+        <v>0.4166</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1158</v>
+        <v>0.1116</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2467</v>
+        <v>-0.2779</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4324</v>
+        <v>0.4166</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4324</v>
+        <v>0.4166</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4324</v>
+        <v>0.4166</v>
       </c>
       <c r="I46" t="n">
         <v>0.453</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3944</v>
+        <v>0.3743</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1056</v>
+        <v>0.1002</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.262</v>
+        <v>-0.2948</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3944</v>
+        <v>0.3743</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3944</v>
+        <v>0.3743</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3944</v>
+        <v>0.3743</v>
       </c>
       <c r="I47" t="n">
         <v>0.4209</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3824</v>
+        <v>0.3697</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1024</v>
+        <v>0.099</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2669</v>
+        <v>-0.2966</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3824</v>
+        <v>0.3697</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3824</v>
+        <v>0.3697</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3824</v>
+        <v>0.3697</v>
       </c>
       <c r="I48" t="n">
         <v>0.3987</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3211</v>
+        <v>0.3163</v>
       </c>
       <c r="C49" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0847</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2916</v>
+        <v>-0.3179</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3211</v>
+        <v>0.3163</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3211</v>
+        <v>0.3163</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3211</v>
+        <v>0.3163</v>
       </c>
       <c r="I49" t="n">
         <v>0.3271</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.297</v>
+        <v>0.2893</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0795</v>
+        <v>0.0775</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3014</v>
+        <v>-0.3287</v>
       </c>
       <c r="E50" t="n">
-        <v>0.297</v>
+        <v>0.2893</v>
       </c>
       <c r="F50" t="n">
-        <v>0.297</v>
+        <v>0.2893</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.297</v>
+        <v>0.2893</v>
       </c>
       <c r="I50" t="n">
         <v>0.3068</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.234</v>
+        <v>0.2297</v>
       </c>
       <c r="C51" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0615</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3268</v>
+        <v>-0.3524</v>
       </c>
       <c r="E51" t="n">
-        <v>0.234</v>
+        <v>0.2297</v>
       </c>
       <c r="F51" t="n">
-        <v>0.234</v>
+        <v>0.2297</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.234</v>
+        <v>0.2297</v>
       </c>
       <c r="I51" t="n">
         <v>0.2395</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.065</v>
+        <v>0.0635</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0174</v>
+        <v>0.017</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3951</v>
+        <v>-0.4186</v>
       </c>
       <c r="E52" t="n">
-        <v>0.065</v>
+        <v>0.0635</v>
       </c>
       <c r="F52" t="n">
-        <v>0.065</v>
+        <v>0.0635</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.065</v>
+        <v>0.0635</v>
       </c>
       <c r="I52" t="n">
         <v>0.0668</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0283</v>
+        <v>-0.0279</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0076</v>
+        <v>-0.0075</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4328</v>
+        <v>-0.455</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0283</v>
+        <v>-0.0279</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0283</v>
+        <v>-0.0279</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0283</v>
+        <v>-0.0279</v>
       </c>
       <c r="I53" t="n">
         <v>-0.0288</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0164</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.446</v>
+        <v>-0.4683</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0611</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1527</v>
+        <v>-0.1515</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0409</v>
+        <v>-0.0406</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.483</v>
+        <v>-0.5043</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1527</v>
+        <v>-0.1515</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1527</v>
+        <v>-0.1515</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1527</v>
+        <v>-0.1515</v>
       </c>
       <c r="I55" t="n">
         <v>-0.1541</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2594</v>
+        <v>-0.2556</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5262</v>
+        <v>-0.5457</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2594</v>
+        <v>-0.2556</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2594</v>
+        <v>-0.2556</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2594</v>
+        <v>-0.2556</v>
       </c>
       <c r="I56" t="n">
         <v>-0.2643</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sorrow</t>
+          <t>la3euka</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.323</v>
+        <v>-0.2752</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0737</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5518</v>
+        <v>-0.5536</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.323</v>
+        <v>-0.2752</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.323</v>
+        <v>-0.2752</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.323</v>
+        <v>-0.2752</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.323</v>
+        <v>-0.2822</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.323</v>
+        <v>-0.2822</v>
       </c>
       <c r="N57" t="n">
-        <v>112</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>la3euka</t>
+          <t>sorrow</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3424</v>
+        <v>-0.323</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0917</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5597</v>
+        <v>-0.5726</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3424</v>
+        <v>-0.323</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3424</v>
+        <v>-0.323</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3424</v>
+        <v>-0.323</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3472</v>
+        <v>-0.323</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>208</v>
+        <v>112</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3472</v>
+        <v>-0.323</v>
       </c>
       <c r="N58" t="n">
-        <v>208</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3564</v>
+        <v>-0.3498</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0955</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5653</v>
+        <v>-0.5833</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3564</v>
+        <v>-0.3498</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3564</v>
+        <v>-0.3498</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3564</v>
+        <v>-0.3498</v>
       </c>
       <c r="I59" t="n">
         <v>-0.3648</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4795</v>
+        <v>-0.4741</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1284</v>
+        <v>-0.127</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6151</v>
+        <v>-0.6328</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4795</v>
+        <v>-0.4741</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4795</v>
+        <v>-0.4741</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4795</v>
+        <v>-0.4741</v>
       </c>
       <c r="I60" t="n">
         <v>-0.4862</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5158</v>
+        <v>-0.5119</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1381</v>
+        <v>-0.1371</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6297</v>
+        <v>-0.6479</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5158</v>
+        <v>-0.5119</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5158</v>
+        <v>-0.5119</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5158</v>
+        <v>-0.5119</v>
       </c>
       <c r="I61" t="n">
         <v>-0.5206</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5563</v>
+        <v>-0.549</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.149</v>
+        <v>-0.147</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6461</v>
+        <v>-0.6626</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5563</v>
+        <v>-0.549</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5563</v>
+        <v>-0.549</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5563</v>
+        <v>-0.549</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5641</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5641</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="N62" t="n">
         <v>208</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7038</v>
+        <v>-0.6934</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1885</v>
+        <v>-0.1857</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7057</v>
+        <v>-0.7202</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7038</v>
+        <v>-0.6934</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7038</v>
+        <v>-0.6934</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7038</v>
+        <v>-0.6934</v>
       </c>
       <c r="I63" t="n">
         <v>-0.717</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8186</v>
+        <v>-0.8034</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2192</v>
+        <v>-0.2152</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7521</v>
+        <v>-0.764</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8186</v>
+        <v>-0.8034</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8186</v>
+        <v>-0.8034</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8186</v>
+        <v>-0.8034</v>
       </c>
       <c r="I64" t="n">
         <v>-0.8378</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8245</v>
+        <v>-0.8184</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2208</v>
+        <v>-0.2192</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7544</v>
+        <v>-0.77</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8245</v>
+        <v>-0.8184</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8245</v>
+        <v>-0.8184</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8245</v>
+        <v>-0.8184</v>
       </c>
       <c r="I65" t="n">
         <v>-0.8322000000000001</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8605</v>
+        <v>-0.8227</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2305</v>
+        <v>-0.2203</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.769</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8605</v>
+        <v>-0.8227</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8605</v>
+        <v>-0.8227</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8605</v>
+        <v>-0.8227</v>
       </c>
       <c r="I66" t="n">
         <v>-0.9098000000000001</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9306</v>
+        <v>-0.9203</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2492</v>
+        <v>-0.2465</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7973</v>
+        <v>-0.8106</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9306</v>
+        <v>-0.9203</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9306</v>
+        <v>-0.9203</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.9306</v>
+        <v>-0.9203</v>
       </c>
       <c r="I67" t="n">
         <v>-0.9437</v>
@@ -3538,7 +3538,7 @@
         <v>-0.2574</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8096</v>
+        <v>-0.8268</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9611</v>
@@ -3584,7 +3584,7 @@
         <v>-0.265</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.8381</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9895</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0952</v>
+        <v>-1.0669</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2933</v>
+        <v>-0.2857</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8638</v>
+        <v>-0.869</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0952</v>
+        <v>-1.0669</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0952</v>
+        <v>-1.0669</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0952</v>
+        <v>-1.0669</v>
       </c>
       <c r="I70" t="n">
         <v>-1.1314</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.143</v>
+        <v>-1.1052</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3061</v>
+        <v>-0.296</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8831</v>
+        <v>-0.8842</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.143</v>
+        <v>-1.1052</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.143</v>
+        <v>-1.1052</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.143</v>
+        <v>-1.1052</v>
       </c>
       <c r="I71" t="n">
         <v>-1.1918</v>
@@ -3722,7 +3722,7 @@
         <v>-0.3626</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.9832</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3537</v>
@@ -3768,7 +3768,7 @@
         <v>-0.4356</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0784</v>
+        <v>-1.0919</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6265</v>
@@ -3814,7 +3814,7 @@
         <v>-0.4493</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.099</v>
+        <v>-1.1122</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6774</v>
@@ -3860,7 +3860,7 @@
         <v>-0.455</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1076</v>
+        <v>-1.1207</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6987</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.9004</v>
+        <v>-1.8375</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.509</v>
+        <v>-0.4921</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1891</v>
+        <v>-1.176</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.9004</v>
+        <v>-1.8375</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.9004</v>
+        <v>-1.8375</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.9004</v>
+        <v>-1.8375</v>
       </c>
       <c r="I76" t="n">
         <v>-1.9815</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9164</v>
+        <v>-1.8879</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5133</v>
+        <v>-0.5056</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1955</v>
+        <v>-1.196</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9164</v>
+        <v>-1.8879</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9164</v>
+        <v>-1.8879</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9164</v>
+        <v>-1.8879</v>
       </c>
       <c r="I77" t="n">
         <v>-1.9523</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.2072</v>
+        <v>-2.199</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.589</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.313</v>
+        <v>-1.32</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.2072</v>
+        <v>-2.199</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.2072</v>
+        <v>-2.199</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.2072</v>
+        <v>-2.199</v>
       </c>
       <c r="I78" t="n">
         <v>-2.2175</v>
@@ -4044,7 +4044,7 @@
         <v>-0.6966</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4721</v>
+        <v>-1.4801</v>
       </c>
       <c r="E79" t="n">
         <v>-2.6009</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.7057</v>
+        <v>-2.6457</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7247</v>
+        <v>-0.7086</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5144</v>
+        <v>-1.498</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.7057</v>
+        <v>-2.6457</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.7057</v>
+        <v>-2.6457</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.7057</v>
+        <v>-2.6457</v>
       </c>
       <c r="I80" t="n">
         <v>-2.7821</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.2346</v>
+        <v>-3.0697</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.8663</v>
+        <v>-0.8222</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7281</v>
+        <v>-1.6669</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.2346</v>
+        <v>-3.0697</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.2346</v>
+        <v>-3.0697</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.2346</v>
+        <v>-3.0697</v>
       </c>
       <c r="I81" t="n">
         <v>-3.4519</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.6124</v>
+        <v>-3.454</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.9675</v>
+        <v>-0.9251</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8807</v>
+        <v>-1.82</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.6124</v>
+        <v>-3.454</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.6124</v>
+        <v>-3.454</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.6124</v>
+        <v>-3.454</v>
       </c>
       <c r="I82" t="n">
         <v>-3.8194</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-3.8564</v>
+        <v>-3.8277</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.0329</v>
+        <v>-1.0252</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.9793</v>
+        <v>-1.9689</v>
       </c>
       <c r="E83" t="n">
-        <v>-3.8564</v>
+        <v>-3.8277</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.8564</v>
+        <v>-3.8277</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.8564</v>
+        <v>-3.8277</v>
       </c>
       <c r="I83" t="n">
         <v>-3.8924</v>
